--- a/curiculam_CE.xlsx
+++ b/curiculam_CE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E728F20F-3519-47F8-A9AD-015049490D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EA77B5-1BA0-4BE3-B723-DCD0A730CB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="5100" windowWidth="17925" windowHeight="10305" activeTab="6" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
+    <workbookView xWindow="5745" yWindow="3330" windowWidth="20370" windowHeight="10110" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
   </bookViews>
   <sheets>
     <sheet name="s1" sheetId="1" r:id="rId1"/>
@@ -1167,7 +1167,7 @@
         <v>185</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1245,7 +1245,7 @@
         <v>185</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>2</v>
